--- a/test/hello.xlsx
+++ b/test/hello.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AutomateDoc\DocAutomate\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E944BA34-2C46-462B-852E-7F856B726502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EADE163-78B8-470C-A432-9B3D8DCE98AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="42">
   <si>
     <t>Very High</t>
   </si>
@@ -66,12 +66,6 @@
     <t>Zone 3</t>
   </si>
   <si>
-    <t>Zone 4</t>
-  </si>
-  <si>
-    <t>Zone 5</t>
-  </si>
-  <si>
     <t>VH</t>
   </si>
   <si>
@@ -79,6 +73,93 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>Step1</t>
+  </si>
+  <si>
+    <t>Step2</t>
+  </si>
+  <si>
+    <t>Step3</t>
+  </si>
+  <si>
+    <t>Step4</t>
+  </si>
+  <si>
+    <t>Fan Operation</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Fan Map</t>
+  </si>
+  <si>
+    <t>Z0</t>
+  </si>
+  <si>
+    <t>Z1</t>
+  </si>
+  <si>
+    <t>Z2</t>
+  </si>
+  <si>
+    <t>Z3</t>
+  </si>
+  <si>
+    <t>Z4</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>-1.0</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -88,10 +169,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -132,12 +219,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -419,156 +525,617 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:C19"/>
+  <dimension ref="A2:I32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="E3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="1">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2">
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="1">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="1" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="1">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2">
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="1" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="1">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="1" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="1">
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
+      <c r="G18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="1" t="s">
+      <c r="G23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>14</v>
+      <c r="G28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="A15:A19"/>
+  <mergeCells count="24">
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="E28:E32"/>
+    <mergeCell ref="F28:F32"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="D8:D17"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="F13:F17"/>
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="A3:A17"/>
+    <mergeCell ref="C8:C17"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F8:F12"/>
+    <mergeCell ref="A18:A32"/>
+    <mergeCell ref="B18:B32"/>
+    <mergeCell ref="D18:D32"/>
+    <mergeCell ref="C18:C32"/>
+    <mergeCell ref="F18:F22"/>
+    <mergeCell ref="E18:E22"/>
+    <mergeCell ref="E23:E27"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>